--- a/tame_output/ON/bt/strategyON_20240208.xlsx
+++ b/tame_output/ON/bt/strategyON_20240208.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,16 +926,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-155.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>127.7%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.5%</t>
+          <t>121.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1866"/>
+  <dimension ref="A1:G1867"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.304126150306436</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44479,6 +44479,29 @@
       </c>
       <c r="G1866" t="n">
         <v>4.463487715892259</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" s="2" t="n">
+        <v>45329</v>
+      </c>
+      <c r="B1867" t="n">
+        <v>3.343651070251906</v>
+      </c>
+      <c r="C1867" t="n">
+        <v>3.118878693692689</v>
+      </c>
+      <c r="D1867" t="n">
+        <v>1.639423217980499</v>
+      </c>
+      <c r="E1867" t="n">
+        <v>3.774291556571141</v>
+      </c>
+      <c r="F1867" t="n">
+        <v>2.258112854780415</v>
+      </c>
+      <c r="G1867" t="n">
+        <v>4.473746406560938</v>
       </c>
     </row>
   </sheetData>
